--- a/data/vendor-search/results_all_appliances.xlsx
+++ b/data/vendor-search/results_all_appliances.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +488,11 @@
           <t>cpe:2.3:o:smarter:smarter_coffee_maker_1st_generation:-:*:*:*:*:*:*:*|cpe:2.3:h:smarter:smarter_coffee_maker_1st_generation:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>smarter coffee</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,6 +526,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:google:android:*:*:*:*:*:*:*:*|cpe:2.3:h:lg:v60_thin_q_5g:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>lg thinq</t>
         </is>
       </c>
     </row>
